--- a/Pxg data for model - June26.xlsx
+++ b/Pxg data for model - June26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aramcotradingus-my.sharepoint.com/personal/alberto_cantafio_aramcotrading_us/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="8_{B36E857D-9F8B-4D95-8C22-2F588010AD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A053D0AD-39F7-4664-94F3-200934A97C8E}"/>
+  <xr:revisionPtr revIDLastSave="206" documentId="8_{B36E857D-9F8B-4D95-8C22-2F588010AD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78016D83-AFCD-48C4-A3C0-81FF5A4B4678}"/>
   <bookViews>
-    <workbookView xWindow="4500" yWindow="2760" windowWidth="28800" windowHeight="15380" xr2:uid="{3EC3D64F-43CC-40B1-9E10-117CE990C3FD}"/>
+    <workbookView xWindow="5180" yWindow="3440" windowWidth="28800" windowHeight="15380" xr2:uid="{3EC3D64F-43CC-40B1-9E10-117CE990C3FD}"/>
   </bookViews>
   <sheets>
     <sheet name="WTI Sprds" sheetId="1" r:id="rId1"/>
@@ -265,132 +265,132 @@
 <volTypes xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <volType type="realTimeData">
     <main first="bofaddin.rtdserver">
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|11422135839758403132</stp>
         <tr r="G10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|14315573980680918327</stp>
         <tr r="Y10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|14981503572928615608</stp>
         <tr r="V10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|11201438284030949441</stp>
         <tr r="AB10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|10502183802689909694</stp>
         <tr r="B10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|10885294957659751165</stp>
         <tr r="E10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|15142186126282573814</stp>
         <tr r="AG10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|11319891862590325353</stp>
         <tr r="AO10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|11158341048667358325</stp>
         <tr r="S10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|11973928606342887979</stp>
         <tr r="AE10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|11914434694568898448</stp>
         <tr r="AJ10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|14296018678020572211</stp>
         <tr r="P10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|18317545794552690073</stp>
         <tr r="AF10" s="1"/>
       </tp>
     </main>
     <main first="bofaddin.rtdserver">
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|14649918488181331304</stp>
         <tr r="T10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|14181539813507892058</stp>
         <tr r="X10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|15547695906520146449</stp>
         <tr r="Q10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|15635252648995413283</stp>
         <tr r="K10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|12162095424453322793</stp>
         <tr r="N10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|15470519764731019263</stp>
         <tr r="AC10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|11113070008375443150</stp>
         <tr r="R10" s="1"/>
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C6</stp>
@@ -399,8 +399,8 @@
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C7</stp>
@@ -409,8 +409,8 @@
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C4</stp>
@@ -419,8 +419,8 @@
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C5</stp>
@@ -429,8 +429,8 @@
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C2</stp>
@@ -439,8 +439,8 @@
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C3</stp>
@@ -449,8 +449,8 @@
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C8</stp>
@@ -459,8 +459,8 @@
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C9</stp>
@@ -469,24 +469,24 @@
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C14</stp>
         <stp>PX_SETTLE</stp>
         <tr r="N7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C24</stp>
         <stp>PX_SETTLE</stp>
         <tr r="X7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C34</stp>
@@ -495,32 +495,32 @@
       </tp>
     </main>
     <main first="bofaddin.rtdserver">
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|9353389439450115463</stp>
         <tr r="Z10" s="1"/>
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C15</stp>
         <stp>PX_SETTLE</stp>
         <tr r="O7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C25</stp>
         <stp>PX_SETTLE</stp>
         <tr r="Y7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C35</stp>
@@ -529,32 +529,32 @@
       </tp>
     </main>
     <main first="bofaddin.rtdserver">
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|9670727858890877535</stp>
         <tr r="AL10" s="1"/>
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C16</stp>
         <stp>PX_SETTLE</stp>
         <tr r="P7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C26</stp>
         <stp>PX_SETTLE</stp>
         <tr r="Z7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C36</stp>
@@ -563,38 +563,38 @@
       </tp>
     </main>
     <main first="bofaddin.rtdserver">
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|4414008271425224932</stp>
         <tr r="L10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|21656641455582567</stp>
         <tr r="AI10" s="1"/>
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C17</stp>
         <stp>PX_SETTLE</stp>
         <tr r="Q7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C27</stp>
         <stp>PX_SETTLE</stp>
         <tr r="AA7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C37</stp>
@@ -603,32 +603,32 @@
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C10</stp>
         <stp>PX_SETTLE</stp>
         <tr r="J7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C20</stp>
         <stp>PX_SETTLE</stp>
         <tr r="T7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C30</stp>
         <stp>PX_SETTLE</stp>
         <tr r="AD7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C40</stp>
@@ -637,46 +637,46 @@
       </tp>
     </main>
     <main first="bofaddin.rtdserver">
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|2932646117888066454</stp>
         <tr r="J10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|6067728361189656770</stp>
         <tr r="AD10" s="1"/>
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C11</stp>
         <stp>PX_SETTLE</stp>
         <tr r="K7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C21</stp>
         <stp>PX_SETTLE</stp>
         <tr r="U7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C31</stp>
         <stp>PX_SETTLE</stp>
         <tr r="AE7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C41</stp>
@@ -685,32 +685,32 @@
       </tp>
     </main>
     <main first="bofaddin.rtdserver">
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|1887382199424025593</stp>
         <tr r="W10" s="1"/>
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C12</stp>
         <stp>PX_SETTLE</stp>
         <tr r="L7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C22</stp>
         <stp>PX_SETTLE</stp>
         <tr r="V7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C32</stp>
@@ -719,32 +719,32 @@
       </tp>
     </main>
     <main first="bofaddin.rtdserver">
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|9515921627921837819</stp>
         <tr r="AA10" s="1"/>
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C13</stp>
         <stp>PX_SETTLE</stp>
         <tr r="M7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C23</stp>
         <stp>PX_SETTLE</stp>
         <tr r="W7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C33</stp>
@@ -753,56 +753,56 @@
       </tp>
     </main>
     <main first="bofaddin.rtdserver">
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|2005872845908754345</stp>
         <tr r="AN10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|3487477098168167095</stp>
         <tr r="AH10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|8338118744393695870</stp>
         <tr r="F10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|5935603634815100542</stp>
         <tr r="I10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|4166879827696433855</stp>
         <tr r="U10" s="1"/>
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C18</stp>
         <stp>PX_SETTLE</stp>
         <tr r="R7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C28</stp>
         <stp>PX_SETTLE</stp>
         <tr r="AB7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C38</stp>
@@ -811,50 +811,50 @@
       </tp>
     </main>
     <main first="bofaddin.rtdserver">
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|6263444032221289141</stp>
         <tr r="D10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|8603436274212667867</stp>
         <tr r="M10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|7459002023377270310</stp>
         <tr r="H10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|3168717555920679078</stp>
         <tr r="AK10" s="1"/>
       </tp>
     </main>
     <main first="bloomberg.rtd">
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C19</stp>
         <stp>PX_SETTLE</stp>
         <tr r="S7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C29</stp>
         <stp>PX_SETTLE</stp>
         <tr r="AC7" s="1"/>
       </tp>
-      <tp t="s">
-        <v>Settlement Price</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>##V3_BFIELDINFOV12</stp>
         <stp>[Pxg data for model - June26.xlsx]WTI Sprds!R7C39</stp>
@@ -863,20 +863,20 @@
       </tp>
     </main>
     <main first="bofaddin.rtdserver">
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|3709707369687832797</stp>
         <tr r="AM10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|2503375530492790224</stp>
         <tr r="C10" s="1"/>
       </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
         <stp>BDH|3705868244795044903</stp>
         <tr r="O10" s="1"/>
@@ -884,7 +884,7 @@
     </main>
     <main first="bofaddin.rtdserver">
       <tp>
-        <v>-3.53</v>
+        <v>-3.48</v>
         <stp/>
         <stp>BDP|6558601099671933478|22</stp>
         <stp>S:ENCO   1-1 Comdty</stp>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F1">
         <f t="array" ref="F1">_xll.BDP("S:ENCO   1-1 Comdty","LAST_PRICE")</f>
-        <v>-3.53</v>
+        <v>-3.48</v>
       </c>
       <c r="I1" t="s">
         <v>1</v>
@@ -2119,165 +2119,165 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B7">
         <f>_xll.BFieldInfo(B$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="C7" t="str">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <f>_xll.BFieldInfo(C$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="D7" t="str">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <f>_xll.BFieldInfo(D$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="E7" t="str">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <f>_xll.BFieldInfo(E$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="F7" t="str">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <f>_xll.BFieldInfo(F$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="G7" t="str">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <f>_xll.BFieldInfo(G$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="H7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <f>_xll.BFieldInfo(H$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="I7" t="str">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <f>_xll.BFieldInfo(I$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="J7" t="str">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <f>_xll.BFieldInfo(J$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="K7" t="str">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <f>_xll.BFieldInfo(K$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="L7" t="str">
+        <v>0</v>
+      </c>
+      <c r="L7">
         <f>_xll.BFieldInfo(L$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="M7" t="str">
+        <v>0</v>
+      </c>
+      <c r="M7">
         <f>_xll.BFieldInfo(M$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="N7" t="str">
+        <v>0</v>
+      </c>
+      <c r="N7">
         <f>_xll.BFieldInfo(N$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="O7" t="str">
+        <v>0</v>
+      </c>
+      <c r="O7">
         <f>_xll.BFieldInfo(O$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="P7" t="str">
+        <v>0</v>
+      </c>
+      <c r="P7">
         <f>_xll.BFieldInfo(P$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="Q7" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q7">
         <f>_xll.BFieldInfo(Q$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="R7" t="str">
+        <v>0</v>
+      </c>
+      <c r="R7">
         <f>_xll.BFieldInfo(R$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="S7" t="str">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <f>_xll.BFieldInfo(S$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="T7" t="str">
+        <v>0</v>
+      </c>
+      <c r="T7">
         <f>_xll.BFieldInfo(T$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="U7" t="str">
+        <v>0</v>
+      </c>
+      <c r="U7">
         <f>_xll.BFieldInfo(U$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="V7" t="str">
+        <v>0</v>
+      </c>
+      <c r="V7">
         <f>_xll.BFieldInfo(V$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="W7" t="str">
+        <v>0</v>
+      </c>
+      <c r="W7">
         <f>_xll.BFieldInfo(W$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="X7" t="str">
+        <v>0</v>
+      </c>
+      <c r="X7">
         <f>_xll.BFieldInfo(X$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="Y7" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y7">
         <f>_xll.BFieldInfo(Y$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="Z7" t="str">
+        <v>0</v>
+      </c>
+      <c r="Z7">
         <f>_xll.BFieldInfo(Z$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="AA7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA7">
         <f>_xll.BFieldInfo(AA$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="AB7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AB7">
         <f>_xll.BFieldInfo(AB$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="AC7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC7">
         <f>_xll.BFieldInfo(AC$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="AD7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AD7">
         <f>_xll.BFieldInfo(AD$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="AE7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE7">
         <f>_xll.BFieldInfo(AE$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="AF7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF7">
         <f>_xll.BFieldInfo(AF$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="AG7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG7">
         <f>_xll.BFieldInfo(AG$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="AH7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AH7">
         <f>_xll.BFieldInfo(AH$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="AI7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI7">
         <f>_xll.BFieldInfo(AI$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="AJ7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
         <f>_xll.BFieldInfo(AJ$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="AK7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AK7">
         <f>_xll.BFieldInfo(AK$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="AL7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AL7">
         <f>_xll.BFieldInfo(AL$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="AM7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM7">
         <f>_xll.BFieldInfo(AM$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="AN7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN7">
         <f>_xll.BFieldInfo(AN$9)</f>
-        <v>Settlement Price</v>
-      </c>
-      <c r="AO7" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO7">
         <f>_xll.BFieldInfo(AO$9)</f>
-        <v>Settlement Price</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.35">
@@ -10773,7 +10773,7 @@
     </row>
     <row r="76" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
-        <f t="shared" ref="A76:A130" si="6">WORKDAY(A75,1)</f>
+        <f t="shared" ref="A76:A139" si="6">WORKDAY(A75,1)</f>
         <v>45751</v>
       </c>
       <c r="B76">
@@ -17537,6 +17537,10 @@
       </c>
     </row>
     <row r="131" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A131" s="1">
+        <f t="shared" si="6"/>
+        <v>45828</v>
+      </c>
       <c r="B131">
         <v>0.49</v>
       </c>
@@ -17656,6 +17660,10 @@
       </c>
     </row>
     <row r="132" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A132" s="1">
+        <f t="shared" si="6"/>
+        <v>45831</v>
+      </c>
       <c r="B132">
         <v>0.49</v>
       </c>
@@ -17775,6 +17783,10 @@
       </c>
     </row>
     <row r="133" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A133" s="1">
+        <f t="shared" si="6"/>
+        <v>45832</v>
+      </c>
       <c r="B133">
         <v>0.49</v>
       </c>
@@ -17894,6 +17906,10 @@
       </c>
     </row>
     <row r="134" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A134" s="1">
+        <f t="shared" si="6"/>
+        <v>45833</v>
+      </c>
       <c r="B134">
         <v>0.49</v>
       </c>
@@ -18013,6 +18029,10 @@
       </c>
     </row>
     <row r="135" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A135" s="1">
+        <f t="shared" si="6"/>
+        <v>45834</v>
+      </c>
       <c r="B135">
         <v>0.49</v>
       </c>
@@ -18132,6 +18152,10 @@
       </c>
     </row>
     <row r="136" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A136" s="1">
+        <f t="shared" si="6"/>
+        <v>45835</v>
+      </c>
       <c r="B136">
         <v>0.49</v>
       </c>
@@ -18251,6 +18275,10 @@
       </c>
     </row>
     <row r="137" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A137" s="1">
+        <f t="shared" si="6"/>
+        <v>45838</v>
+      </c>
       <c r="B137">
         <v>0.49</v>
       </c>
@@ -18370,6 +18398,10 @@
       </c>
     </row>
     <row r="138" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A138" s="1">
+        <f t="shared" si="6"/>
+        <v>45839</v>
+      </c>
       <c r="B138">
         <v>0.49</v>
       </c>
@@ -18489,6 +18521,10 @@
       </c>
     </row>
     <row r="139" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A139" s="1">
+        <f t="shared" si="6"/>
+        <v>45840</v>
+      </c>
       <c r="B139">
         <v>0.49</v>
       </c>
@@ -18608,6 +18644,10 @@
       </c>
     </row>
     <row r="140" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A140" s="1">
+        <f t="shared" ref="A140:A203" si="7">WORKDAY(A139,1)</f>
+        <v>45841</v>
+      </c>
       <c r="B140">
         <v>0.49</v>
       </c>
@@ -18727,6 +18767,10 @@
       </c>
     </row>
     <row r="141" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A141" s="1">
+        <f t="shared" si="7"/>
+        <v>45842</v>
+      </c>
       <c r="B141">
         <v>0.49</v>
       </c>
@@ -18846,6 +18890,10 @@
       </c>
     </row>
     <row r="142" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A142" s="1">
+        <f t="shared" si="7"/>
+        <v>45845</v>
+      </c>
       <c r="B142">
         <v>0.49</v>
       </c>
@@ -18965,6 +19013,10 @@
       </c>
     </row>
     <row r="143" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A143" s="1">
+        <f t="shared" si="7"/>
+        <v>45846</v>
+      </c>
       <c r="B143">
         <v>0.49</v>
       </c>
@@ -19084,6 +19136,10 @@
       </c>
     </row>
     <row r="144" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A144" s="1">
+        <f t="shared" si="7"/>
+        <v>45847</v>
+      </c>
       <c r="B144">
         <v>0.49</v>
       </c>
@@ -19202,7 +19258,11 @@
         <v>-0.03</v>
       </c>
     </row>
-    <row r="145" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A145" s="1">
+        <f t="shared" si="7"/>
+        <v>45848</v>
+      </c>
       <c r="B145">
         <v>0.49</v>
       </c>
@@ -19321,7 +19381,11 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="146" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A146" s="1">
+        <f t="shared" si="7"/>
+        <v>45849</v>
+      </c>
       <c r="B146">
         <v>0.49</v>
       </c>
@@ -19440,7 +19504,11 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="147" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A147" s="1">
+        <f t="shared" si="7"/>
+        <v>45852</v>
+      </c>
       <c r="B147">
         <v>0.49</v>
       </c>
@@ -19559,7 +19627,11 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="148" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A148" s="1">
+        <f t="shared" si="7"/>
+        <v>45853</v>
+      </c>
       <c r="B148">
         <v>0.49</v>
       </c>
@@ -19678,7 +19750,11 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="149" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A149" s="1">
+        <f t="shared" si="7"/>
+        <v>45854</v>
+      </c>
       <c r="B149">
         <v>0.49</v>
       </c>
@@ -19797,7 +19873,11 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="150" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A150" s="1">
+        <f t="shared" si="7"/>
+        <v>45855</v>
+      </c>
       <c r="B150">
         <v>0.49</v>
       </c>
@@ -19916,7 +19996,11 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="151" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A151" s="1">
+        <f t="shared" si="7"/>
+        <v>45856</v>
+      </c>
       <c r="B151">
         <v>0.49</v>
       </c>
@@ -20035,7 +20119,11 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="152" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A152" s="1">
+        <f t="shared" si="7"/>
+        <v>45859</v>
+      </c>
       <c r="B152">
         <v>0.49</v>
       </c>
@@ -20154,7 +20242,11 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="153" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A153" s="1">
+        <f t="shared" si="7"/>
+        <v>45860</v>
+      </c>
       <c r="B153">
         <v>0.49</v>
       </c>
@@ -20273,7 +20365,11 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="154" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A154" s="1">
+        <f t="shared" si="7"/>
+        <v>45861</v>
+      </c>
       <c r="B154">
         <v>0.49</v>
       </c>
@@ -20392,7 +20488,11 @@
         <v>-0.03</v>
       </c>
     </row>
-    <row r="155" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A155" s="1">
+        <f t="shared" si="7"/>
+        <v>45862</v>
+      </c>
       <c r="B155">
         <v>0.49</v>
       </c>
@@ -20511,7 +20611,11 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="156" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A156" s="1">
+        <f t="shared" si="7"/>
+        <v>45863</v>
+      </c>
       <c r="B156">
         <v>0.49</v>
       </c>
@@ -20630,7 +20734,11 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="157" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A157" s="1">
+        <f t="shared" si="7"/>
+        <v>45866</v>
+      </c>
       <c r="B157">
         <v>0.49</v>
       </c>
@@ -20749,7 +20857,11 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="158" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A158" s="1">
+        <f t="shared" si="7"/>
+        <v>45867</v>
+      </c>
       <c r="B158">
         <v>0.49</v>
       </c>
@@ -20868,7 +20980,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A159" s="1">
+        <f t="shared" si="7"/>
+        <v>45868</v>
+      </c>
       <c r="B159">
         <v>0.49</v>
       </c>
@@ -20987,7 +21103,11 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="160" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A160" s="1">
+        <f t="shared" si="7"/>
+        <v>45869</v>
+      </c>
       <c r="B160">
         <v>0.49</v>
       </c>
@@ -21106,7 +21226,11 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="161" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A161" s="1">
+        <f t="shared" si="7"/>
+        <v>45870</v>
+      </c>
       <c r="B161">
         <v>0.49</v>
       </c>
@@ -21225,7 +21349,11 @@
         <v>-0.03</v>
       </c>
     </row>
-    <row r="162" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A162" s="1">
+        <f t="shared" si="7"/>
+        <v>45873</v>
+      </c>
       <c r="B162">
         <v>0.49</v>
       </c>
@@ -21344,7 +21472,11 @@
         <v>-0.03</v>
       </c>
     </row>
-    <row r="163" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A163" s="1">
+        <f t="shared" si="7"/>
+        <v>45874</v>
+      </c>
       <c r="B163">
         <v>0.49</v>
       </c>
@@ -21463,7 +21595,11 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="164" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A164" s="1">
+        <f t="shared" si="7"/>
+        <v>45875</v>
+      </c>
       <c r="B164">
         <v>0.49</v>
       </c>
@@ -21582,7 +21718,11 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="165" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A165" s="1">
+        <f t="shared" si="7"/>
+        <v>45876</v>
+      </c>
       <c r="B165">
         <v>0.49</v>
       </c>
@@ -21701,7 +21841,11 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="166" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A166" s="1">
+        <f t="shared" si="7"/>
+        <v>45877</v>
+      </c>
       <c r="B166">
         <v>0.49</v>
       </c>
@@ -21820,7 +21964,11 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="167" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A167" s="1">
+        <f t="shared" si="7"/>
+        <v>45880</v>
+      </c>
       <c r="B167">
         <v>0.49</v>
       </c>
@@ -21939,7 +22087,11 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="168" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A168" s="1">
+        <f t="shared" si="7"/>
+        <v>45881</v>
+      </c>
       <c r="B168">
         <v>0.49</v>
       </c>
@@ -22058,7 +22210,11 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="169" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A169" s="1">
+        <f t="shared" si="7"/>
+        <v>45882</v>
+      </c>
       <c r="B169">
         <v>0.49</v>
       </c>
@@ -22177,7 +22333,11 @@
         <v>-0.03</v>
       </c>
     </row>
-    <row r="170" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A170" s="1">
+        <f t="shared" si="7"/>
+        <v>45883</v>
+      </c>
       <c r="B170">
         <v>0.49</v>
       </c>
@@ -22296,7 +22456,11 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="171" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A171" s="1">
+        <f t="shared" si="7"/>
+        <v>45884</v>
+      </c>
       <c r="B171">
         <v>0.49</v>
       </c>
@@ -22415,7 +22579,11 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="172" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A172" s="1">
+        <f t="shared" si="7"/>
+        <v>45887</v>
+      </c>
       <c r="B172">
         <v>0.49</v>
       </c>
@@ -22534,7 +22702,11 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="173" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A173" s="1">
+        <f t="shared" si="7"/>
+        <v>45888</v>
+      </c>
       <c r="B173">
         <v>0.49</v>
       </c>
@@ -22653,7 +22825,11 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="174" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A174" s="1">
+        <f t="shared" si="7"/>
+        <v>45889</v>
+      </c>
       <c r="B174">
         <v>0.49</v>
       </c>
@@ -22772,7 +22948,11 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="175" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A175" s="1">
+        <f t="shared" si="7"/>
+        <v>45890</v>
+      </c>
       <c r="B175">
         <v>0.49</v>
       </c>
@@ -22891,7 +23071,11 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="176" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A176" s="1">
+        <f t="shared" si="7"/>
+        <v>45891</v>
+      </c>
       <c r="B176">
         <v>0.49</v>
       </c>
@@ -23010,7 +23194,11 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="177" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A177" s="1">
+        <f t="shared" si="7"/>
+        <v>45894</v>
+      </c>
       <c r="B177">
         <v>0.49</v>
       </c>
@@ -23129,7 +23317,11 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="178" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A178" s="1">
+        <f t="shared" si="7"/>
+        <v>45895</v>
+      </c>
       <c r="B178">
         <v>0.49</v>
       </c>
@@ -23248,7 +23440,11 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="179" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A179" s="1">
+        <f t="shared" si="7"/>
+        <v>45896</v>
+      </c>
       <c r="B179">
         <v>0.49</v>
       </c>
@@ -23367,7 +23563,11 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="180" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A180" s="1">
+        <f t="shared" si="7"/>
+        <v>45897</v>
+      </c>
       <c r="B180">
         <v>0.49</v>
       </c>
@@ -23486,7 +23686,11 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="181" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A181" s="1">
+        <f t="shared" si="7"/>
+        <v>45898</v>
+      </c>
       <c r="B181">
         <v>0.49</v>
       </c>
@@ -23605,7 +23809,11 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="182" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A182" s="1">
+        <f t="shared" si="7"/>
+        <v>45901</v>
+      </c>
       <c r="B182">
         <v>0.49</v>
       </c>
@@ -23724,7 +23932,11 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="183" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A183" s="1">
+        <f t="shared" si="7"/>
+        <v>45902</v>
+      </c>
       <c r="B183">
         <v>0.49</v>
       </c>
@@ -23843,7 +24055,11 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="184" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A184" s="1">
+        <f t="shared" si="7"/>
+        <v>45903</v>
+      </c>
       <c r="B184">
         <v>0.49</v>
       </c>
@@ -23962,7 +24178,11 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="185" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A185" s="1">
+        <f t="shared" si="7"/>
+        <v>45904</v>
+      </c>
       <c r="B185">
         <v>0.49</v>
       </c>
@@ -24081,7 +24301,11 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="186" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A186" s="1">
+        <f t="shared" si="7"/>
+        <v>45905</v>
+      </c>
       <c r="B186">
         <v>0.49</v>
       </c>
@@ -24200,7 +24424,11 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="187" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A187" s="1">
+        <f t="shared" si="7"/>
+        <v>45908</v>
+      </c>
       <c r="B187">
         <v>0.49</v>
       </c>
@@ -24319,7 +24547,11 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="188" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A188" s="1">
+        <f t="shared" si="7"/>
+        <v>45909</v>
+      </c>
       <c r="B188">
         <v>0.49</v>
       </c>
@@ -24438,7 +24670,11 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="189" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A189" s="1">
+        <f t="shared" si="7"/>
+        <v>45910</v>
+      </c>
       <c r="B189">
         <v>0.49</v>
       </c>
@@ -24557,7 +24793,11 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="190" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A190" s="1">
+        <f t="shared" si="7"/>
+        <v>45911</v>
+      </c>
       <c r="B190">
         <v>0.49</v>
       </c>
@@ -24676,7 +24916,11 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="191" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A191" s="1">
+        <f t="shared" si="7"/>
+        <v>45912</v>
+      </c>
       <c r="B191">
         <v>0.49</v>
       </c>
@@ -24795,7 +25039,11 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="192" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A192" s="1">
+        <f t="shared" si="7"/>
+        <v>45915</v>
+      </c>
       <c r="B192">
         <v>0.49</v>
       </c>
@@ -24914,7 +25162,11 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="193" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A193" s="1">
+        <f t="shared" si="7"/>
+        <v>45916</v>
+      </c>
       <c r="B193">
         <v>0.49</v>
       </c>
@@ -25033,7 +25285,11 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="194" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A194" s="1">
+        <f t="shared" si="7"/>
+        <v>45917</v>
+      </c>
       <c r="B194">
         <v>0.49</v>
       </c>
@@ -25152,7 +25408,11 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="195" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A195" s="1">
+        <f t="shared" si="7"/>
+        <v>45918</v>
+      </c>
       <c r="B195">
         <v>0.49</v>
       </c>
@@ -25271,7 +25531,11 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="196" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A196" s="1">
+        <f t="shared" si="7"/>
+        <v>45919</v>
+      </c>
       <c r="B196">
         <v>0.49</v>
       </c>
@@ -25390,7 +25654,11 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="197" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A197" s="1">
+        <f t="shared" si="7"/>
+        <v>45922</v>
+      </c>
       <c r="B197">
         <v>0.49</v>
       </c>
@@ -25509,7 +25777,11 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="198" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A198" s="1">
+        <f t="shared" si="7"/>
+        <v>45923</v>
+      </c>
       <c r="B198">
         <v>0.49</v>
       </c>
@@ -25628,7 +25900,11 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="199" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A199" s="1">
+        <f t="shared" si="7"/>
+        <v>45924</v>
+      </c>
       <c r="B199">
         <v>0.49</v>
       </c>
@@ -25747,7 +26023,11 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="200" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A200" s="1">
+        <f t="shared" si="7"/>
+        <v>45925</v>
+      </c>
       <c r="B200">
         <v>0.49</v>
       </c>
@@ -25866,7 +26146,11 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="201" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A201" s="1">
+        <f t="shared" si="7"/>
+        <v>45926</v>
+      </c>
       <c r="B201">
         <v>0.49</v>
       </c>
@@ -25985,7 +26269,11 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="202" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A202" s="1">
+        <f t="shared" si="7"/>
+        <v>45929</v>
+      </c>
       <c r="B202">
         <v>0.49</v>
       </c>
@@ -26104,7 +26392,11 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="203" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A203" s="1">
+        <f t="shared" si="7"/>
+        <v>45930</v>
+      </c>
       <c r="B203">
         <v>0.49</v>
       </c>
@@ -26223,7 +26515,11 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="204" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A204" s="1">
+        <f t="shared" ref="A204:A267" si="8">WORKDAY(A203,1)</f>
+        <v>45931</v>
+      </c>
       <c r="B204">
         <v>0.49</v>
       </c>
@@ -26342,7 +26638,11 @@
         <v>-0.12</v>
       </c>
     </row>
-    <row r="205" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A205" s="1">
+        <f t="shared" si="8"/>
+        <v>45932</v>
+      </c>
       <c r="B205">
         <v>0.49</v>
       </c>
@@ -26461,7 +26761,11 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="206" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A206" s="1">
+        <f t="shared" si="8"/>
+        <v>45933</v>
+      </c>
       <c r="B206">
         <v>0.49</v>
       </c>
@@ -26580,7 +26884,11 @@
         <v>-0.12</v>
       </c>
     </row>
-    <row r="207" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A207" s="1">
+        <f t="shared" si="8"/>
+        <v>45936</v>
+      </c>
       <c r="B207">
         <v>0.49</v>
       </c>
@@ -26699,7 +27007,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="208" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A208" s="1">
+        <f t="shared" si="8"/>
+        <v>45937</v>
+      </c>
       <c r="B208">
         <v>0.49</v>
       </c>
@@ -26818,7 +27130,11 @@
         <v>-0.12</v>
       </c>
     </row>
-    <row r="209" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A209" s="1">
+        <f t="shared" si="8"/>
+        <v>45938</v>
+      </c>
       <c r="B209">
         <v>0.49</v>
       </c>
@@ -26937,7 +27253,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="210" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A210" s="1">
+        <f t="shared" si="8"/>
+        <v>45939</v>
+      </c>
       <c r="B210">
         <v>0.49</v>
       </c>
@@ -27056,7 +27376,11 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="211" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A211" s="1">
+        <f t="shared" si="8"/>
+        <v>45940</v>
+      </c>
       <c r="B211">
         <v>0.49</v>
       </c>
@@ -27175,7 +27499,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="212" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A212" s="1">
+        <f t="shared" si="8"/>
+        <v>45943</v>
+      </c>
       <c r="B212">
         <v>0.49</v>
       </c>
@@ -27294,7 +27622,11 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="213" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A213" s="1">
+        <f t="shared" si="8"/>
+        <v>45944</v>
+      </c>
       <c r="B213">
         <v>0.49</v>
       </c>
@@ -27413,7 +27745,11 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="214" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A214" s="1">
+        <f t="shared" si="8"/>
+        <v>45945</v>
+      </c>
       <c r="B214">
         <v>0.49</v>
       </c>
@@ -27532,7 +27868,11 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="215" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A215" s="1">
+        <f t="shared" si="8"/>
+        <v>45946</v>
+      </c>
       <c r="B215">
         <v>0.49</v>
       </c>
@@ -27651,7 +27991,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="216" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A216" s="1">
+        <f t="shared" si="8"/>
+        <v>45947</v>
+      </c>
       <c r="B216">
         <v>0.49</v>
       </c>
@@ -27770,7 +28114,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="217" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A217" s="1">
+        <f t="shared" si="8"/>
+        <v>45950</v>
+      </c>
       <c r="B217">
         <v>0.49</v>
       </c>
@@ -27889,7 +28237,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="218" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A218" s="1">
+        <f t="shared" si="8"/>
+        <v>45951</v>
+      </c>
       <c r="B218">
         <v>0.49</v>
       </c>
@@ -28008,7 +28360,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="219" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A219" s="1">
+        <f t="shared" si="8"/>
+        <v>45952</v>
+      </c>
       <c r="B219">
         <v>0.49</v>
       </c>
@@ -28127,7 +28483,11 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="220" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A220" s="1">
+        <f t="shared" si="8"/>
+        <v>45953</v>
+      </c>
       <c r="B220">
         <v>0.49</v>
       </c>
@@ -28246,7 +28606,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="221" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A221" s="1">
+        <f t="shared" si="8"/>
+        <v>45954</v>
+      </c>
       <c r="B221">
         <v>0.49</v>
       </c>
@@ -28365,7 +28729,11 @@
         <v>-0.12</v>
       </c>
     </row>
-    <row r="222" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A222" s="1">
+        <f t="shared" si="8"/>
+        <v>45957</v>
+      </c>
       <c r="B222">
         <v>0.49</v>
       </c>
@@ -28484,7 +28852,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="223" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A223" s="1">
+        <f t="shared" si="8"/>
+        <v>45958</v>
+      </c>
       <c r="B223">
         <v>0.49</v>
       </c>
@@ -28603,7 +28975,11 @@
         <v>-0.12</v>
       </c>
     </row>
-    <row r="224" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A224" s="1">
+        <f t="shared" si="8"/>
+        <v>45959</v>
+      </c>
       <c r="B224">
         <v>0.49</v>
       </c>
@@ -28722,7 +29098,11 @@
         <v>-0.12</v>
       </c>
     </row>
-    <row r="225" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A225" s="1">
+        <f t="shared" si="8"/>
+        <v>45960</v>
+      </c>
       <c r="B225">
         <v>0.49</v>
       </c>
@@ -28841,7 +29221,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="226" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A226" s="1">
+        <f t="shared" si="8"/>
+        <v>45961</v>
+      </c>
       <c r="B226">
         <v>0.49</v>
       </c>
@@ -28960,7 +29344,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="227" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A227" s="1">
+        <f t="shared" si="8"/>
+        <v>45964</v>
+      </c>
       <c r="B227">
         <v>0.49</v>
       </c>
@@ -29079,7 +29467,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="228" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A228" s="1">
+        <f t="shared" si="8"/>
+        <v>45965</v>
+      </c>
       <c r="B228">
         <v>0.49</v>
       </c>
@@ -29198,7 +29590,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="229" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A229" s="1">
+        <f t="shared" si="8"/>
+        <v>45966</v>
+      </c>
       <c r="B229">
         <v>0.49</v>
       </c>
@@ -29317,7 +29713,11 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="230" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A230" s="1">
+        <f t="shared" si="8"/>
+        <v>45967</v>
+      </c>
       <c r="B230">
         <v>0.49</v>
       </c>
@@ -29436,7 +29836,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="231" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A231" s="1">
+        <f t="shared" si="8"/>
+        <v>45968</v>
+      </c>
       <c r="B231">
         <v>0.49</v>
       </c>
@@ -29555,7 +29959,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="232" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A232" s="1">
+        <f t="shared" si="8"/>
+        <v>45971</v>
+      </c>
       <c r="B232">
         <v>0.49</v>
       </c>
@@ -29674,7 +30082,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="233" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A233" s="1">
+        <f t="shared" si="8"/>
+        <v>45972</v>
+      </c>
       <c r="B233">
         <v>0.49</v>
       </c>
@@ -29793,7 +30205,11 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="234" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A234" s="1">
+        <f t="shared" si="8"/>
+        <v>45973</v>
+      </c>
       <c r="B234">
         <v>0.49</v>
       </c>
@@ -29912,7 +30328,11 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="235" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A235" s="1">
+        <f t="shared" si="8"/>
+        <v>45974</v>
+      </c>
       <c r="B235">
         <v>0.49</v>
       </c>
@@ -30031,7 +30451,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="236" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A236" s="1">
+        <f t="shared" si="8"/>
+        <v>45975</v>
+      </c>
       <c r="B236">
         <v>0.49</v>
       </c>
@@ -30150,7 +30574,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="237" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A237" s="1">
+        <f t="shared" si="8"/>
+        <v>45978</v>
+      </c>
       <c r="B237">
         <v>0.49</v>
       </c>
@@ -30269,7 +30697,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="238" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A238" s="1">
+        <f t="shared" si="8"/>
+        <v>45979</v>
+      </c>
       <c r="B238">
         <v>0.49</v>
       </c>
@@ -30388,7 +30820,11 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="239" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A239" s="1">
+        <f t="shared" si="8"/>
+        <v>45980</v>
+      </c>
       <c r="B239">
         <v>0.49</v>
       </c>
@@ -30507,7 +30943,11 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="240" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A240" s="1">
+        <f t="shared" si="8"/>
+        <v>45981</v>
+      </c>
       <c r="B240">
         <v>0.49</v>
       </c>
@@ -30626,7 +31066,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="241" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A241" s="1">
+        <f t="shared" si="8"/>
+        <v>45982</v>
+      </c>
       <c r="B241">
         <v>0.49</v>
       </c>
@@ -30745,7 +31189,11 @@
         <v>-0.15</v>
       </c>
     </row>
-    <row r="242" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A242" s="1">
+        <f t="shared" si="8"/>
+        <v>45985</v>
+      </c>
       <c r="B242">
         <v>0.49</v>
       </c>
@@ -30864,7 +31312,11 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="243" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A243" s="1">
+        <f t="shared" si="8"/>
+        <v>45986</v>
+      </c>
       <c r="B243">
         <v>0.49</v>
       </c>
@@ -30983,7 +31435,11 @@
         <v>-0.16</v>
       </c>
     </row>
-    <row r="244" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A244" s="1">
+        <f t="shared" si="8"/>
+        <v>45987</v>
+      </c>
       <c r="B244">
         <v>0.49</v>
       </c>
@@ -31102,7 +31558,11 @@
         <v>-0.15</v>
       </c>
     </row>
-    <row r="245" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A245" s="1">
+        <f t="shared" si="8"/>
+        <v>45988</v>
+      </c>
       <c r="B245">
         <v>0.49</v>
       </c>
@@ -31221,7 +31681,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="246" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A246" s="1">
+        <f t="shared" si="8"/>
+        <v>45989</v>
+      </c>
       <c r="B246">
         <v>0.49</v>
       </c>
@@ -31340,7 +31804,11 @@
         <v>-0.15</v>
       </c>
     </row>
-    <row r="247" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A247" s="1">
+        <f t="shared" si="8"/>
+        <v>45992</v>
+      </c>
       <c r="B247">
         <v>0.49</v>
       </c>
@@ -31459,7 +31927,11 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="248" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A248" s="1">
+        <f t="shared" si="8"/>
+        <v>45993</v>
+      </c>
       <c r="B248">
         <v>0.49</v>
       </c>
@@ -31578,7 +32050,11 @@
         <v>-0.15</v>
       </c>
     </row>
-    <row r="249" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A249" s="1">
+        <f t="shared" si="8"/>
+        <v>45994</v>
+      </c>
       <c r="B249">
         <v>0.49</v>
       </c>
@@ -31697,7 +32173,11 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="250" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A250" s="1">
+        <f t="shared" si="8"/>
+        <v>45995</v>
+      </c>
       <c r="B250">
         <v>0.49</v>
       </c>
@@ -31816,7 +32296,11 @@
         <v>-0.12</v>
       </c>
     </row>
-    <row r="251" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A251" s="1">
+        <f t="shared" si="8"/>
+        <v>45996</v>
+      </c>
       <c r="B251">
         <v>0.49</v>
       </c>
@@ -31935,7 +32419,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="252" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A252" s="1">
+        <f t="shared" si="8"/>
+        <v>45999</v>
+      </c>
       <c r="B252">
         <v>0.49</v>
       </c>
@@ -32054,7 +32542,11 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="253" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A253" s="1">
+        <f t="shared" si="8"/>
+        <v>46000</v>
+      </c>
       <c r="B253">
         <v>0.49</v>
       </c>
@@ -32173,7 +32665,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="254" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A254" s="1">
+        <f t="shared" si="8"/>
+        <v>46001</v>
+      </c>
       <c r="B254">
         <v>0.49</v>
       </c>
@@ -32292,7 +32788,11 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="255" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A255" s="1">
+        <f t="shared" si="8"/>
+        <v>46002</v>
+      </c>
       <c r="B255">
         <v>0.49</v>
       </c>
@@ -32411,7 +32911,11 @@
         <v>-0.15</v>
       </c>
     </row>
-    <row r="256" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A256" s="1">
+        <f t="shared" si="8"/>
+        <v>46003</v>
+      </c>
       <c r="B256">
         <v>0.49</v>
       </c>
@@ -32530,7 +33034,11 @@
         <v>-0.16</v>
       </c>
     </row>
-    <row r="257" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A257" s="1">
+        <f t="shared" si="8"/>
+        <v>46006</v>
+      </c>
       <c r="B257">
         <v>0.49</v>
       </c>
@@ -32649,7 +33157,11 @@
         <v>-0.18</v>
       </c>
     </row>
-    <row r="258" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A258" s="1">
+        <f t="shared" si="8"/>
+        <v>46007</v>
+      </c>
       <c r="B258">
         <v>0.49</v>
       </c>
@@ -32768,7 +33280,11 @@
         <v>-0.18</v>
       </c>
     </row>
-    <row r="259" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A259" s="1">
+        <f t="shared" si="8"/>
+        <v>46008</v>
+      </c>
       <c r="B259">
         <v>0.49</v>
       </c>
@@ -32887,7 +33403,11 @@
         <v>-0.17</v>
       </c>
     </row>
-    <row r="260" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A260" s="1">
+        <f t="shared" si="8"/>
+        <v>46009</v>
+      </c>
       <c r="B260">
         <v>0.49</v>
       </c>
@@ -33006,7 +33526,11 @@
         <v>-0.17</v>
       </c>
     </row>
-    <row r="261" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A261" s="1">
+        <f t="shared" si="8"/>
+        <v>46010</v>
+      </c>
       <c r="B261">
         <v>0.49</v>
       </c>
@@ -33125,7 +33649,11 @@
         <v>-0.17</v>
       </c>
     </row>
-    <row r="262" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A262" s="1">
+        <f t="shared" si="8"/>
+        <v>46013</v>
+      </c>
       <c r="B262">
         <v>0.49</v>
       </c>
@@ -33244,7 +33772,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="263" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A263" s="1">
+        <f t="shared" si="8"/>
+        <v>46014</v>
+      </c>
       <c r="B263">
         <v>0.49</v>
       </c>
@@ -33363,7 +33895,11 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="264" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A264" s="1">
+        <f t="shared" si="8"/>
+        <v>46015</v>
+      </c>
       <c r="B264">
         <v>0.49</v>
       </c>
@@ -33482,7 +34018,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="265" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A265" s="1">
+        <f t="shared" si="8"/>
+        <v>46016</v>
+      </c>
       <c r="B265">
         <v>0.49</v>
       </c>
@@ -33601,7 +34141,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="266" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A266" s="1">
+        <f t="shared" si="8"/>
+        <v>46017</v>
+      </c>
       <c r="B266">
         <v>0.49</v>
       </c>
@@ -33720,7 +34264,11 @@
         <v>-0.17</v>
       </c>
     </row>
-    <row r="267" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A267" s="1">
+        <f t="shared" si="8"/>
+        <v>46020</v>
+      </c>
       <c r="B267">
         <v>0.49</v>
       </c>
@@ -33839,7 +34387,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="268" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A268" s="1">
+        <f t="shared" ref="A268:A331" si="9">WORKDAY(A267,1)</f>
+        <v>46021</v>
+      </c>
       <c r="B268">
         <v>0.49</v>
       </c>
@@ -33958,7 +34510,11 @@
         <v>-0.15</v>
       </c>
     </row>
-    <row r="269" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A269" s="1">
+        <f t="shared" si="9"/>
+        <v>46022</v>
+      </c>
       <c r="B269">
         <v>0.49</v>
       </c>
@@ -34077,7 +34633,11 @@
         <v>-0.15</v>
       </c>
     </row>
-    <row r="270" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A270" s="1">
+        <f t="shared" si="9"/>
+        <v>46023</v>
+      </c>
       <c r="B270">
         <v>0.49</v>
       </c>
@@ -34196,7 +34756,11 @@
         <v>-0.15</v>
       </c>
     </row>
-    <row r="271" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A271" s="1">
+        <f t="shared" si="9"/>
+        <v>46024</v>
+      </c>
       <c r="B271">
         <v>0.49</v>
       </c>
@@ -34315,7 +34879,11 @@
         <v>-0.16</v>
       </c>
     </row>
-    <row r="272" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A272" s="1">
+        <f t="shared" si="9"/>
+        <v>46027</v>
+      </c>
       <c r="B272">
         <v>0.49</v>
       </c>
@@ -34434,7 +35002,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="273" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A273" s="1">
+        <f t="shared" si="9"/>
+        <v>46028</v>
+      </c>
       <c r="B273">
         <v>0.49</v>
       </c>
@@ -34553,7 +35125,11 @@
         <v>-0.15</v>
       </c>
     </row>
-    <row r="274" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A274" s="1">
+        <f t="shared" si="9"/>
+        <v>46029</v>
+      </c>
       <c r="B274">
         <v>0.49</v>
       </c>
@@ -34672,7 +35248,11 @@
         <v>-0.16</v>
       </c>
     </row>
-    <row r="275" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A275" s="1">
+        <f t="shared" si="9"/>
+        <v>46030</v>
+      </c>
       <c r="B275">
         <v>0.49</v>
       </c>
@@ -34791,7 +35371,11 @@
         <v>-0.15</v>
       </c>
     </row>
-    <row r="276" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A276" s="1">
+        <f t="shared" si="9"/>
+        <v>46031</v>
+      </c>
       <c r="B276">
         <v>0.49</v>
       </c>
@@ -34910,7 +35494,11 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="277" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A277" s="1">
+        <f t="shared" si="9"/>
+        <v>46034</v>
+      </c>
       <c r="B277">
         <v>0.49</v>
       </c>
@@ -35029,7 +35617,11 @@
         <v>-0.12</v>
       </c>
     </row>
-    <row r="278" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A278" s="1">
+        <f t="shared" si="9"/>
+        <v>46035</v>
+      </c>
       <c r="B278">
         <v>0.49</v>
       </c>
@@ -35148,7 +35740,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="279" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A279" s="1">
+        <f t="shared" si="9"/>
+        <v>46036</v>
+      </c>
       <c r="B279">
         <v>0.49</v>
       </c>
@@ -35267,7 +35863,11 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="280" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A280" s="1">
+        <f t="shared" si="9"/>
+        <v>46037</v>
+      </c>
       <c r="B280">
         <v>0.49</v>
       </c>
@@ -35386,7 +35986,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="281" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A281" s="1">
+        <f t="shared" si="9"/>
+        <v>46038</v>
+      </c>
       <c r="B281">
         <v>0.49</v>
       </c>
@@ -35505,7 +36109,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="282" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A282" s="1">
+        <f t="shared" si="9"/>
+        <v>46041</v>
+      </c>
       <c r="B282">
         <v>0.49</v>
       </c>
@@ -35624,7 +36232,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="283" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A283" s="1">
+        <f t="shared" si="9"/>
+        <v>46042</v>
+      </c>
       <c r="B283">
         <v>0.49</v>
       </c>
@@ -35743,7 +36355,11 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="284" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A284" s="1">
+        <f t="shared" si="9"/>
+        <v>46043</v>
+      </c>
       <c r="B284">
         <v>0.49</v>
       </c>
@@ -35862,7 +36478,11 @@
         <v>-0.12</v>
       </c>
     </row>
-    <row r="285" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A285" s="1">
+        <f t="shared" si="9"/>
+        <v>46044</v>
+      </c>
       <c r="B285">
         <v>0.49</v>
       </c>
@@ -35981,7 +36601,11 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="286" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A286" s="1">
+        <f t="shared" si="9"/>
+        <v>46045</v>
+      </c>
       <c r="B286">
         <v>0.49</v>
       </c>
@@ -36100,7 +36724,11 @@
         <v>-0.12</v>
       </c>
     </row>
-    <row r="287" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A287" s="1">
+        <f t="shared" si="9"/>
+        <v>46048</v>
+      </c>
       <c r="B287">
         <v>0.49</v>
       </c>
@@ -36219,7 +36847,11 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="288" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A288" s="1">
+        <f t="shared" si="9"/>
+        <v>46049</v>
+      </c>
       <c r="B288">
         <v>0.49</v>
       </c>
@@ -36338,7 +36970,11 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="289" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A289" s="1">
+        <f t="shared" si="9"/>
+        <v>46050</v>
+      </c>
       <c r="B289">
         <v>0.49</v>
       </c>
@@ -36457,7 +37093,11 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="290" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A290" s="1">
+        <f t="shared" si="9"/>
+        <v>46051</v>
+      </c>
       <c r="B290">
         <v>0.49</v>
       </c>
@@ -36576,7 +37216,11 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="291" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A291" s="1">
+        <f t="shared" si="9"/>
+        <v>46052</v>
+      </c>
       <c r="B291">
         <v>0.49</v>
       </c>
@@ -36695,7 +37339,11 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="292" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A292" s="1">
+        <f t="shared" si="9"/>
+        <v>46055</v>
+      </c>
       <c r="B292">
         <v>0.49</v>
       </c>
@@ -36814,7 +37462,11 @@
         <v>-0.12</v>
       </c>
     </row>
-    <row r="293" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A293" s="1">
+        <f t="shared" si="9"/>
+        <v>46056</v>
+      </c>
       <c r="B293">
         <v>0.49</v>
       </c>
@@ -36933,7 +37585,11 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="294" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A294" s="1">
+        <f t="shared" si="9"/>
+        <v>46057</v>
+      </c>
       <c r="B294">
         <v>0.49</v>
       </c>
@@ -37052,7 +37708,11 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="295" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A295" s="1">
+        <f t="shared" si="9"/>
+        <v>46058</v>
+      </c>
       <c r="B295">
         <v>0.49</v>
       </c>
@@ -37171,7 +37831,11 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="296" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A296" s="1">
+        <f t="shared" si="9"/>
+        <v>46059</v>
+      </c>
       <c r="B296">
         <v>0.49</v>
       </c>
@@ -37290,7 +37954,11 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="297" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A297" s="1">
+        <f t="shared" si="9"/>
+        <v>46062</v>
+      </c>
       <c r="B297">
         <v>0.49</v>
       </c>
@@ -37409,7 +38077,11 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="298" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A298" s="1">
+        <f t="shared" si="9"/>
+        <v>46063</v>
+      </c>
       <c r="B298">
         <v>0.49</v>
       </c>
@@ -37528,7 +38200,11 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="299" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A299" s="1">
+        <f t="shared" si="9"/>
+        <v>46064</v>
+      </c>
       <c r="B299">
         <v>0.49</v>
       </c>
@@ -37647,7 +38323,11 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="300" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A300" s="1">
+        <f t="shared" si="9"/>
+        <v>46065</v>
+      </c>
       <c r="B300">
         <v>0.49</v>
       </c>
@@ -37766,7 +38446,11 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="301" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A301" s="1">
+        <f t="shared" si="9"/>
+        <v>46066</v>
+      </c>
       <c r="B301">
         <v>0.49</v>
       </c>
@@ -37885,7 +38569,11 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="302" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A302" s="1">
+        <f t="shared" si="9"/>
+        <v>46069</v>
+      </c>
       <c r="B302">
         <v>0.49</v>
       </c>
@@ -38004,7 +38692,11 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="303" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A303" s="1">
+        <f t="shared" si="9"/>
+        <v>46070</v>
+      </c>
       <c r="B303">
         <v>0.49</v>
       </c>
@@ -38123,7 +38815,11 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="304" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A304" s="1">
+        <f t="shared" si="9"/>
+        <v>46071</v>
+      </c>
       <c r="B304">
         <v>0.49</v>
       </c>
@@ -38242,7 +38938,11 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="305" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A305" s="1">
+        <f t="shared" si="9"/>
+        <v>46072</v>
+      </c>
       <c r="B305">
         <v>0.49</v>
       </c>
@@ -38361,7 +39061,11 @@
         <v>-0.03</v>
       </c>
     </row>
-    <row r="306" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A306" s="1">
+        <f t="shared" si="9"/>
+        <v>46073</v>
+      </c>
       <c r="B306">
         <v>0.49</v>
       </c>
@@ -38480,7 +39184,11 @@
         <v>-0.03</v>
       </c>
     </row>
-    <row r="307" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A307" s="1">
+        <f t="shared" si="9"/>
+        <v>46076</v>
+      </c>
       <c r="B307">
         <v>0.49</v>
       </c>
@@ -38599,7 +39307,11 @@
         <v>-0.03</v>
       </c>
     </row>
-    <row r="308" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A308" s="1">
+        <f t="shared" si="9"/>
+        <v>46077</v>
+      </c>
       <c r="B308">
         <v>0.49</v>
       </c>
@@ -38718,7 +39430,11 @@
         <v>-0.03</v>
       </c>
     </row>
-    <row r="309" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A309" s="1">
+        <f t="shared" si="9"/>
+        <v>46078</v>
+      </c>
       <c r="B309">
         <v>0.49</v>
       </c>
@@ -38837,7 +39553,11 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="310" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A310" s="1">
+        <f t="shared" si="9"/>
+        <v>46079</v>
+      </c>
       <c r="B310">
         <v>0.49</v>
       </c>
@@ -38956,7 +39676,11 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="311" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A311" s="1">
+        <f t="shared" si="9"/>
+        <v>46080</v>
+      </c>
       <c r="B311">
         <v>0.49</v>
       </c>
@@ -39075,7 +39799,11 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="312" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A312" s="1">
+        <f t="shared" si="9"/>
+        <v>46083</v>
+      </c>
       <c r="B312">
         <v>0.49</v>
       </c>
@@ -39194,7 +39922,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A313" s="1">
+        <f t="shared" si="9"/>
+        <v>46084</v>
+      </c>
       <c r="B313">
         <v>0.49</v>
       </c>
@@ -39313,7 +40045,11 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="314" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A314" s="1">
+        <f t="shared" si="9"/>
+        <v>46085</v>
+      </c>
       <c r="B314">
         <v>0.49</v>
       </c>
@@ -39432,7 +40168,11 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="315" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A315" s="1">
+        <f t="shared" si="9"/>
+        <v>46086</v>
+      </c>
       <c r="B315">
         <v>0.49</v>
       </c>
@@ -39551,7 +40291,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A316" s="1">
+        <f t="shared" si="9"/>
+        <v>46087</v>
+      </c>
       <c r="B316">
         <v>0.49</v>
       </c>
@@ -39670,7 +40414,11 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="317" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A317" s="1">
+        <f t="shared" si="9"/>
+        <v>46090</v>
+      </c>
       <c r="B317">
         <v>0.49</v>
       </c>
@@ -39789,7 +40537,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="318" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A318" s="1">
+        <f t="shared" si="9"/>
+        <v>46091</v>
+      </c>
       <c r="B318">
         <v>0.49</v>
       </c>
@@ -39908,7 +40660,11 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="319" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A319" s="1">
+        <f t="shared" si="9"/>
+        <v>46092</v>
+      </c>
       <c r="B319">
         <v>0.49</v>
       </c>
@@ -40027,7 +40783,11 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="320" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A320" s="1">
+        <f t="shared" si="9"/>
+        <v>46093</v>
+      </c>
       <c r="B320">
         <v>0.49</v>
       </c>
@@ -40146,7 +40906,11 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="321" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A321" s="1">
+        <f t="shared" si="9"/>
+        <v>46094</v>
+      </c>
       <c r="B321">
         <v>0.49</v>
       </c>
@@ -40265,7 +41029,11 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="322" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A322" s="1">
+        <f t="shared" si="9"/>
+        <v>46097</v>
+      </c>
       <c r="B322">
         <v>0.49</v>
       </c>
@@ -40384,7 +41152,11 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="323" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A323" s="1">
+        <f t="shared" si="9"/>
+        <v>46098</v>
+      </c>
       <c r="B323">
         <v>0.49</v>
       </c>
@@ -40503,7 +41275,11 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="324" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A324" s="1">
+        <f t="shared" si="9"/>
+        <v>46099</v>
+      </c>
       <c r="B324">
         <v>0.49</v>
       </c>
@@ -40622,7 +41398,11 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="325" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A325" s="1">
+        <f t="shared" si="9"/>
+        <v>46100</v>
+      </c>
       <c r="B325">
         <v>0.49</v>
       </c>
@@ -40741,7 +41521,11 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="326" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A326" s="1">
+        <f t="shared" si="9"/>
+        <v>46101</v>
+      </c>
       <c r="B326">
         <v>0.49</v>
       </c>
@@ -40860,7 +41644,11 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="327" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A327" s="1">
+        <f t="shared" si="9"/>
+        <v>46104</v>
+      </c>
       <c r="B327">
         <v>0.49</v>
       </c>
@@ -40979,7 +41767,11 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="328" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A328" s="1">
+        <f t="shared" si="9"/>
+        <v>46105</v>
+      </c>
       <c r="B328">
         <v>0.49</v>
       </c>
@@ -41098,7 +41890,11 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="329" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A329" s="1">
+        <f t="shared" si="9"/>
+        <v>46106</v>
+      </c>
       <c r="B329">
         <v>0.49</v>
       </c>
@@ -41217,7 +42013,11 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="330" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A330" s="1">
+        <f t="shared" si="9"/>
+        <v>46107</v>
+      </c>
       <c r="B330">
         <v>0.49</v>
       </c>
@@ -41336,7 +42136,11 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="331" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A331" s="1">
+        <f t="shared" si="9"/>
+        <v>46108</v>
+      </c>
       <c r="B331">
         <v>0.49</v>
       </c>
@@ -41455,7 +42259,11 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="332" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A332" s="1">
+        <f t="shared" ref="A332:A394" si="10">WORKDAY(A331,1)</f>
+        <v>46111</v>
+      </c>
       <c r="B332">
         <v>0.49</v>
       </c>
@@ -41574,7 +42382,11 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="333" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A333" s="1">
+        <f t="shared" si="10"/>
+        <v>46112</v>
+      </c>
       <c r="B333">
         <v>0.49</v>
       </c>
@@ -41693,7 +42505,11 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="334" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A334" s="1">
+        <f t="shared" si="10"/>
+        <v>46113</v>
+      </c>
       <c r="B334">
         <v>0.49</v>
       </c>
@@ -41812,7 +42628,11 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="335" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A335" s="1">
+        <f t="shared" si="10"/>
+        <v>46114</v>
+      </c>
       <c r="B335">
         <v>0.49</v>
       </c>
@@ -41931,7 +42751,11 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="336" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A336" s="1">
+        <f t="shared" si="10"/>
+        <v>46115</v>
+      </c>
       <c r="B336">
         <v>0.49</v>
       </c>
@@ -42050,7 +42874,11 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="337" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A337" s="1">
+        <f t="shared" si="10"/>
+        <v>46118</v>
+      </c>
       <c r="B337">
         <v>0.49</v>
       </c>
@@ -42169,7 +42997,11 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="338" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A338" s="1">
+        <f t="shared" si="10"/>
+        <v>46119</v>
+      </c>
       <c r="B338">
         <v>0.49</v>
       </c>
@@ -42288,7 +43120,11 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="339" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A339" s="1">
+        <f t="shared" si="10"/>
+        <v>46120</v>
+      </c>
       <c r="B339">
         <v>0.49</v>
       </c>
@@ -42407,7 +43243,11 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="340" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A340" s="1">
+        <f t="shared" si="10"/>
+        <v>46121</v>
+      </c>
       <c r="B340">
         <v>0.49</v>
       </c>
@@ -42526,7 +43366,11 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="341" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A341" s="1">
+        <f t="shared" si="10"/>
+        <v>46122</v>
+      </c>
       <c r="B341">
         <v>0.49</v>
       </c>
@@ -42645,7 +43489,11 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="342" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A342" s="1">
+        <f t="shared" si="10"/>
+        <v>46125</v>
+      </c>
       <c r="B342">
         <v>0.49</v>
       </c>
@@ -42764,7 +43612,11 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="343" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A343" s="1">
+        <f t="shared" si="10"/>
+        <v>46126</v>
+      </c>
       <c r="B343">
         <v>0.49</v>
       </c>
@@ -42883,7 +43735,11 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="344" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A344" s="1">
+        <f t="shared" si="10"/>
+        <v>46127</v>
+      </c>
       <c r="B344">
         <v>0.49</v>
       </c>
@@ -43002,7 +43858,11 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="345" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A345" s="1">
+        <f t="shared" si="10"/>
+        <v>46128</v>
+      </c>
       <c r="B345">
         <v>0.49</v>
       </c>
@@ -43121,7 +43981,11 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="346" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A346" s="1">
+        <f t="shared" si="10"/>
+        <v>46129</v>
+      </c>
       <c r="B346">
         <v>0.49</v>
       </c>
@@ -43240,7 +44104,11 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="347" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A347" s="1">
+        <f t="shared" si="10"/>
+        <v>46132</v>
+      </c>
       <c r="B347">
         <v>0.49</v>
       </c>
@@ -43359,7 +44227,11 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="348" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A348" s="1">
+        <f t="shared" si="10"/>
+        <v>46133</v>
+      </c>
       <c r="B348">
         <v>0.49</v>
       </c>
@@ -43478,7 +44350,11 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="349" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A349" s="1">
+        <f t="shared" si="10"/>
+        <v>46134</v>
+      </c>
       <c r="B349">
         <v>0.49</v>
       </c>
@@ -43597,7 +44473,11 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="350" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A350" s="1">
+        <f t="shared" si="10"/>
+        <v>46135</v>
+      </c>
       <c r="B350">
         <v>0.49</v>
       </c>
@@ -43716,7 +44596,11 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="351" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A351" s="1">
+        <f t="shared" si="10"/>
+        <v>46136</v>
+      </c>
       <c r="B351">
         <v>0.49</v>
       </c>
@@ -43835,7 +44719,11 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="352" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A352" s="1">
+        <f t="shared" si="10"/>
+        <v>46139</v>
+      </c>
       <c r="B352">
         <v>0.49</v>
       </c>
@@ -43954,7 +44842,11 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="353" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A353" s="1">
+        <f t="shared" si="10"/>
+        <v>46140</v>
+      </c>
       <c r="B353">
         <v>0.49</v>
       </c>
@@ -44073,7 +44965,11 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="354" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A354" s="1">
+        <f t="shared" si="10"/>
+        <v>46141</v>
+      </c>
       <c r="B354">
         <v>0.49</v>
       </c>
@@ -44192,7 +45088,11 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="355" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A355" s="1">
+        <f t="shared" si="10"/>
+        <v>46142</v>
+      </c>
       <c r="B355">
         <v>0.49</v>
       </c>
@@ -44311,7 +45211,11 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="356" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A356" s="1">
+        <f t="shared" si="10"/>
+        <v>46143</v>
+      </c>
       <c r="B356">
         <v>0.49</v>
       </c>
@@ -44430,7 +45334,11 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="357" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A357" s="1">
+        <f t="shared" si="10"/>
+        <v>46146</v>
+      </c>
       <c r="B357">
         <v>0.49</v>
       </c>
@@ -44549,7 +45457,11 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="358" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A358" s="1">
+        <f t="shared" si="10"/>
+        <v>46147</v>
+      </c>
       <c r="B358">
         <v>0.49</v>
       </c>
@@ -44668,7 +45580,11 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="359" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A359" s="1">
+        <f t="shared" si="10"/>
+        <v>46148</v>
+      </c>
       <c r="B359">
         <v>0.49</v>
       </c>
@@ -44787,7 +45703,11 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="360" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A360" s="1">
+        <f t="shared" si="10"/>
+        <v>46149</v>
+      </c>
       <c r="B360">
         <v>0.49</v>
       </c>
@@ -44906,7 +45826,11 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="361" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A361" s="1">
+        <f t="shared" si="10"/>
+        <v>46150</v>
+      </c>
       <c r="B361">
         <v>0.49</v>
       </c>
@@ -45025,7 +45949,11 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="362" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A362" s="1">
+        <f t="shared" si="10"/>
+        <v>46153</v>
+      </c>
       <c r="B362">
         <v>0.49</v>
       </c>
@@ -45144,7 +46072,11 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="363" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A363" s="1">
+        <f t="shared" si="10"/>
+        <v>46154</v>
+      </c>
       <c r="B363">
         <v>0.49</v>
       </c>
@@ -45263,7 +46195,11 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="364" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A364" s="1">
+        <f t="shared" si="10"/>
+        <v>46155</v>
+      </c>
       <c r="B364">
         <v>0.49</v>
       </c>
@@ -45382,7 +46318,11 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="365" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A365" s="1">
+        <f t="shared" si="10"/>
+        <v>46156</v>
+      </c>
       <c r="B365">
         <v>0.49</v>
       </c>
@@ -45501,7 +46441,11 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="366" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A366" s="1">
+        <f t="shared" si="10"/>
+        <v>46157</v>
+      </c>
       <c r="B366">
         <v>0.49</v>
       </c>
@@ -45620,7 +46564,11 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="367" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A367" s="1">
+        <f t="shared" si="10"/>
+        <v>46160</v>
+      </c>
       <c r="B367">
         <v>0.49</v>
       </c>
@@ -45739,7 +46687,11 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="368" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A368" s="1">
+        <f t="shared" si="10"/>
+        <v>46161</v>
+      </c>
       <c r="B368">
         <v>0.49</v>
       </c>
@@ -45858,7 +46810,11 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="369" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A369" s="1">
+        <f t="shared" si="10"/>
+        <v>46162</v>
+      </c>
       <c r="B369">
         <v>0.49</v>
       </c>
@@ -45977,7 +46933,11 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="370" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A370" s="1">
+        <f t="shared" si="10"/>
+        <v>46163</v>
+      </c>
       <c r="B370">
         <v>0.49</v>
       </c>
@@ -46096,7 +47056,11 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="371" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A371" s="1">
+        <f t="shared" si="10"/>
+        <v>46164</v>
+      </c>
       <c r="B371">
         <v>0.49</v>
       </c>
@@ -46215,7 +47179,11 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="372" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A372" s="1">
+        <f t="shared" si="10"/>
+        <v>46167</v>
+      </c>
       <c r="B372">
         <v>0.49</v>
       </c>
@@ -46334,7 +47302,11 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="373" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A373" s="1">
+        <f t="shared" si="10"/>
+        <v>46168</v>
+      </c>
       <c r="B373">
         <v>0.49</v>
       </c>
@@ -46453,7 +47425,11 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="374" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A374" s="1">
+        <f t="shared" si="10"/>
+        <v>46169</v>
+      </c>
       <c r="B374">
         <v>0.49</v>
       </c>
@@ -46572,7 +47548,11 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="375" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A375" s="1">
+        <f t="shared" si="10"/>
+        <v>46170</v>
+      </c>
       <c r="B375">
         <v>0.49</v>
       </c>
@@ -46691,7 +47671,11 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="376" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A376" s="1">
+        <f t="shared" si="10"/>
+        <v>46171</v>
+      </c>
       <c r="B376">
         <v>0.49</v>
       </c>
@@ -46810,7 +47794,11 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="377" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A377" s="1">
+        <f t="shared" si="10"/>
+        <v>46174</v>
+      </c>
       <c r="B377">
         <v>0.49</v>
       </c>
@@ -46929,7 +47917,11 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="378" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A378" s="1">
+        <f t="shared" si="10"/>
+        <v>46175</v>
+      </c>
       <c r="B378">
         <v>0.49</v>
       </c>
@@ -47048,7 +48040,11 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="379" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A379" s="1">
+        <f t="shared" si="10"/>
+        <v>46176</v>
+      </c>
       <c r="B379">
         <v>0.49</v>
       </c>
@@ -47167,7 +48163,11 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="380" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A380" s="1">
+        <f t="shared" si="10"/>
+        <v>46177</v>
+      </c>
       <c r="B380">
         <v>0.49</v>
       </c>
@@ -47286,7 +48286,11 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="381" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A381" s="1">
+        <f t="shared" si="10"/>
+        <v>46178</v>
+      </c>
       <c r="B381">
         <v>0.49</v>
       </c>
@@ -47405,7 +48409,11 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="382" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A382" s="1">
+        <f t="shared" si="10"/>
+        <v>46181</v>
+      </c>
       <c r="B382">
         <v>0.49</v>
       </c>
@@ -47524,7 +48532,11 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="383" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A383" s="1">
+        <f t="shared" si="10"/>
+        <v>46182</v>
+      </c>
       <c r="B383">
         <v>0.49</v>
       </c>
@@ -47643,7 +48655,11 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="384" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A384" s="1">
+        <f t="shared" si="10"/>
+        <v>46183</v>
+      </c>
       <c r="B384">
         <v>0.49</v>
       </c>
@@ -47762,7 +48778,11 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="385" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A385" s="1">
+        <f t="shared" si="10"/>
+        <v>46184</v>
+      </c>
       <c r="B385">
         <v>0.49</v>
       </c>
@@ -47881,7 +48901,11 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="386" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A386" s="1">
+        <f t="shared" si="10"/>
+        <v>46185</v>
+      </c>
       <c r="B386">
         <v>0.49</v>
       </c>
@@ -48000,7 +49024,11 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="387" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A387" s="1">
+        <f t="shared" si="10"/>
+        <v>46188</v>
+      </c>
       <c r="B387">
         <v>0.49</v>
       </c>
@@ -48119,7 +49147,11 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="388" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A388" s="1">
+        <f t="shared" si="10"/>
+        <v>46189</v>
+      </c>
       <c r="B388">
         <v>0.49</v>
       </c>
@@ -48238,7 +49270,11 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="389" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A389" s="1">
+        <f t="shared" si="10"/>
+        <v>46190</v>
+      </c>
       <c r="B389">
         <v>0.49</v>
       </c>
@@ -48357,7 +49393,11 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="390" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A390" s="1">
+        <f t="shared" si="10"/>
+        <v>46191</v>
+      </c>
       <c r="B390">
         <v>0.49</v>
       </c>
@@ -48476,7 +49516,11 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="391" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A391" s="1">
+        <f t="shared" si="10"/>
+        <v>46192</v>
+      </c>
       <c r="B391">
         <v>0.49</v>
       </c>
@@ -48595,7 +49639,11 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="392" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A392" s="1">
+        <f t="shared" si="10"/>
+        <v>46195</v>
+      </c>
       <c r="B392">
         <v>0.49</v>
       </c>
@@ -48714,7 +49762,11 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="393" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A393" s="1">
+        <f t="shared" si="10"/>
+        <v>46196</v>
+      </c>
       <c r="B393">
         <v>0.49</v>
       </c>
@@ -48833,7 +49885,11 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="394" spans="2:40" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A394" s="1">
+        <f t="shared" si="10"/>
+        <v>46197</v>
+      </c>
       <c r="B394">
         <v>0.49</v>
       </c>
